--- a/janabril2026_amostra_5x5.xlsx
+++ b/janabril2026_amostra_5x5.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>10380110013</t>
+          <t>10380110013.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>01930260013</t>
+          <t>1930260013.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10380110013</t>
+          <t>10380110013.0</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -879,7 +879,11 @@
           <t>12977432000136</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4966457.0</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>10</t>
@@ -1063,7 +1067,11 @@
           <t>28037401000135</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>10603692.0</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>1033</t>
@@ -1131,7 +1139,11 @@
           <t>08154258000154</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3923614</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>12</t>
